--- a/docs/notices/CAHIER_RECETTE_AUDITS_2026-10-26.xlsx
+++ b/docs/notices/CAHIER_RECETTE_AUDITS_2026-10-26.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="577">
   <si>
     <t>Cahier de recette : corrections des audits de code</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Version testée</t>
   </si>
   <si>
-    <t>Branche PRES-/audits-code-dffa0a, commit 9b02b3c7 (26/10/2026). WAR : target/prestige.war construit à partir de ce commit. Il ne contient pas les commits récents de la branche principale (droits, horloge, bornes, téléphone de la vente).</t>
+    <t>Branche PRES-/audits-code-dffa0a, état du 26/10/2026 au soir (dates VC-12 et VC-16 comprises). WAR : target/prestige.war construit à partir de cet état. Il ne contient pas les commits récents de la branche principale (droits, horloge, bornes, téléphone de la vente).</t>
   </si>
   <si>
     <t>Référence</t>
@@ -79,10 +79,10 @@
     <t>Colonne « Test automatique » : script Playwright du dépôt (src/test/e2e/...), lancé seul, un à la fois : node src/test/e2e/audits/repro-vente-comptant.js. Une ligne FAIL = défaut présent.</t>
   </si>
   <si>
-    <t>Restent en échec</t>
-  </si>
-  <si>
-    <t>VC-12 et VC-16 (cas « hier ») : décision métier en attente sur la date des écritures. Voir l'onglet « Décisions ».</t>
+    <t>Dates des écritures</t>
+  </si>
+  <si>
+    <t>VC-12 et VC-16 : décision du 26/10, les écritures portent la date de l'opération réelle (vente d'origine, date saisie du mouvement).</t>
   </si>
   <si>
     <t>Exemple de saisie</t>
@@ -411,13 +411,13 @@
 3. Comparer les dates de la transaction, de la contre-passation, de la recette et du mouvement de stock.</t>
   </si>
   <si>
-    <t>DÉCISION EN ATTENTE (date de l'opération ou de la saisie) : non corrigé. À jouer pour constat seulement.</t>
+    <t>Toutes les écritures portent la date de la vente d'origine (veille) : transaction de la copie, contre-passation, recette, mouvements de stock de la copie et de l'annulation (décision du 26/10 : date de l'opération réelle). Une modification du jour même reste datée du jour.</t>
   </si>
   <si>
     <t>Transaction et contre-passation datées de la veille ; recette et stock du jour.</t>
   </si>
   <si>
-    <t>repro-vente-comptant.js (VC-12) : reste en échec tant que la décision n'est pas prise</t>
+    <t>repro-vente-comptant.js (VC-12)</t>
   </si>
   <si>
     <t>11</t>
@@ -463,13 +463,13 @@
 2. Puis une entrée de 1 000 F datée d'hier.</t>
   </si>
   <si>
-    <t>Date de demain refusée. Date d'hier : DÉCISION EN ATTENTE (aujourd'hui, mouvement et règlement à hier, transaction au jour).</t>
+    <t>Date de demain refusée avec un message. Date d'hier : mouvement, règlement et transaction de caisse datés d'hier (décision du 26/10 : date saisie du mouvement).</t>
   </si>
   <si>
     <t>Date future acceptée ; dates différentes entre mouvement, règlement et transaction.</t>
   </si>
   <si>
-    <t>repro-remise-caisse.js (VC-16) : le cas « hier » reste en échec tant que la décision n'est pas prise</t>
+    <t>repro-remise-caisse.js (VC-16)</t>
   </si>
   <si>
     <t>13</t>
@@ -1743,10 +1743,7 @@
     <t>VC-12, VC-16</t>
   </si>
   <si>
-    <t>Seules les dates futures sont refusées. Une modification d'une vente de la veille et un mouvement daté d'hier gardent des dates différentes selon l'écriture.</t>
-  </si>
-  <si>
-    <t>Date de l'opération réelle, ou date de la saisie ?</t>
+    <t>Tranché le 26/10 : date de l'opération réelle. Modification d'une vente d'un autre jour : toutes les écritures à la date de la vente d'origine ; mouvement de caisse : date saisie (le futur est refusé).</t>
   </si>
   <si>
     <t>Vente différée réglée puis modifiée</t>
@@ -5478,7 +5475,7 @@
         <v>558</v>
       </c>
       <c r="D2" t="s" s="5">
-        <v>559</v>
+        <v>497</v>
       </c>
       <c r="E2" t="s" s="6">
         <v>52</v>
@@ -5492,16 +5489,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="5">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B3" t="s" s="5">
         <v>424</v>
       </c>
       <c r="C3" t="s" s="5">
+        <v>560</v>
+      </c>
+      <c r="D3" t="s" s="5">
         <v>561</v>
-      </c>
-      <c r="D3" t="s" s="5">
-        <v>562</v>
       </c>
       <c r="E3" t="s" s="6">
         <v>52</v>
@@ -5515,16 +5512,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="5">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B4" t="s" s="5">
         <v>432</v>
       </c>
       <c r="C4" t="s" s="5">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D4" t="s" s="5">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E4" t="s" s="6">
         <v>52</v>
@@ -5538,16 +5535,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="5">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B5" t="s" s="5">
         <v>358</v>
       </c>
       <c r="C5" t="s" s="5">
+        <v>565</v>
+      </c>
+      <c r="D5" t="s" s="5">
         <v>566</v>
-      </c>
-      <c r="D5" t="s" s="5">
-        <v>567</v>
       </c>
       <c r="E5" t="s" s="6">
         <v>52</v>
@@ -5561,13 +5558,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="5">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B6" t="s" s="5">
         <v>202</v>
       </c>
       <c r="C6" t="s" s="5">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D6" t="s" s="5">
         <v>497</v>
@@ -5584,16 +5581,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="5">
+        <v>569</v>
+      </c>
+      <c r="B7" t="s" s="5">
         <v>570</v>
       </c>
-      <c r="B7" t="s" s="5">
+      <c r="C7" t="s" s="5">
         <v>571</v>
       </c>
-      <c r="C7" t="s" s="5">
+      <c r="D7" t="s" s="5">
         <v>572</v>
-      </c>
-      <c r="D7" t="s" s="5">
-        <v>573</v>
       </c>
       <c r="E7" t="s" s="6">
         <v>52</v>
@@ -5607,16 +5604,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="5">
+        <v>573</v>
+      </c>
+      <c r="B8" t="s" s="5">
         <v>574</v>
       </c>
-      <c r="B8" t="s" s="5">
+      <c r="C8" t="s" s="5">
         <v>575</v>
       </c>
-      <c r="C8" t="s" s="5">
+      <c r="D8" t="s" s="5">
         <v>576</v>
-      </c>
-      <c r="D8" t="s" s="5">
-        <v>577</v>
       </c>
       <c r="E8" t="s" s="6">
         <v>52</v>
